--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -588,7 +588,7 @@
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -622,7 +622,7 @@
     <t>Task.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -745,7 +745,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1013,7 +1013,7 @@
     <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
+    <t>http://hl7.org/fhir/ValueSet/task-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -1083,7 +1083,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1215,7 +1215,7 @@
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.role, Request.performerType</t>
@@ -1256,7 +1256,7 @@
     <t>Task.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1323,7 +1323,7 @@
     <t>Task.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1370,7 +1370,7 @@
     <t>Task.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -5796,7 +5796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>297</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>306</v>
       </c>
@@ -10922,12 +10922,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN78">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-task.xlsx
+++ b/fhir/StructureDefinition-ehealth-task.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
